--- a/src/Data/testData.xlsx
+++ b/src/Data/testData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE88161-DF8B-4911-9B45-3C45F5B097B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94EA4C7-9971-4686-891D-059EF189B7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
   <si>
     <t>standard_user</t>
   </si>
   <si>
     <t>secret_sauce</t>
+  </si>
+  <si>
+    <t>standard_users</t>
   </si>
 </sst>
 </file>
@@ -364,17 +367,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>1</v>
       </c>
     </row>
